--- a/public/templates/process-docs/光伏组件支架防腐记录.xlsx
+++ b/public/templates/process-docs/光伏组件支架防腐记录.xlsx
@@ -694,7 +694,7 @@
     <t xml:space="preserve">抽样单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">抽样日期</t>
